--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486930_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486930_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4759</v>
+        <v>3.5714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1219</v>
+        <v>0.1877</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3541</v>
+        <v>3.3837</v>
       </c>
       <c r="G2" t="n">
         <v>-1.09</v>
@@ -610,13 +610,13 @@
         <v>3.2855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3955</v>
+        <v>0.491</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1586</v>
+        <v>0.2245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2369</v>
+        <v>0.2665</v>
       </c>
       <c r="V2" t="n">
         <v>2.117</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2361</v>
+        <v>1.8661</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3944</v>
+        <v>2.9058</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1583</v>
+        <v>-1.0397</v>
       </c>
       <c r="G3" t="n">
         <v>1.0253</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4319</v>
+        <v>-0.802</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7246</v>
+        <v>-0.2132</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7074</v>
+        <v>-0.5888</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0069</v>
+        <v>0.8894</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3035</v>
+        <v>-0.784</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3103</v>
+        <v>1.6733</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3777</v>
+        <v>0.6907</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.07</v>
+        <v>2.5566</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3077</v>
+        <v>-1.866</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6442</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6837</v>
+        <v>1.9958</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0395</v>
+        <v>-1.1717</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7335</v>
+        <v>-0.1334</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3863</v>
+        <v>0.5609</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3472</v>
+        <v>-0.6943</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>2.8748</v>
       </c>
       <c r="S4" t="n">
-        <v>1.017</v>
+        <v>0.7613</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5461</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4709</v>
+        <v>0.1106</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4805</v>
+        <v>-1.1786</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4805</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5937</v>
+        <v>0.8199</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0203</v>
+        <v>-0.3422</v>
       </c>
       <c r="F5" t="n">
-        <v>1.614</v>
+        <v>1.1621</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6907</v>
+        <v>-1.3777</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5566</v>
+        <v>-1.07</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.866</v>
+        <v>-0.3077</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8241000000000001</v>
+        <v>-0.6442</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9958</v>
+        <v>-0.6837</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1717</v>
+        <v>0.0395</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1334</v>
+        <v>-0.7335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5609</v>
+        <v>-0.3863</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6943</v>
+        <v>-0.3472</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8748</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4657</v>
+        <v>0.83</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4144</v>
+        <v>0.5074</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0513</v>
+        <v>0.3226</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4737</v>
+        <v>0.1628</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6422</v>
+        <v>-0.2284</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1685</v>
+        <v>0.3912</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6802</v>
+        <v>-0.9044</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1093</v>
+        <v>2.1479</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4291</v>
+        <v>-3.0523</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.615</v>
+        <v>1.0812</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6939</v>
+        <v>1.9763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0789</v>
+        <v>-0.895</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-1.9856</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4154</v>
+        <v>0.1716</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3502</v>
+        <v>-2.1572</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4095</v>
+        <v>-0.5221</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0272</v>
+        <v>0.2633</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3823</v>
+        <v>-0.7854</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6359</v>
+        <v>-0.4235</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.681</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.2574</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9044</v>
+        <v>-0.6802</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1479</v>
+        <v>-1.1093</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0523</v>
+        <v>0.4291</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0812</v>
+        <v>-0.615</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9763</v>
+        <v>-0.6939</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.895</v>
+        <v>0.0789</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9856</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1716</v>
+        <v>-0.4154</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1572</v>
+        <v>0.3502</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4641</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3209</v>
+        <v>-0.3593</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2094</v>
+        <v>-0.066</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1115</v>
+        <v>-0.2934</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-1.4236</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1087</v>
+        <v>-1.2629</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3683</v>
+        <v>-0.1607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3611</v>
+        <v>-3.1709</v>
       </c>
       <c r="H8" t="n">
-        <v>0.824</v>
+        <v>-1.4501</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4629</v>
+        <v>-1.7208</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4103</v>
+        <v>-2.2903</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3183</v>
+        <v>-0.8691</v>
       </c>
       <c r="L8" t="n">
-        <v>0.092</v>
+        <v>-1.4211</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0491</v>
+        <v>-0.8806</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5057</v>
+        <v>-0.581</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5548</v>
+        <v>-0.2996</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>2.2588</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2855</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9457</v>
+        <v>-0.2712</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0458</v>
+        <v>-0.1513</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8999</v>
+        <v>-0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2259</v>
+        <v>-0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9466</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4367</v>
+        <v>-1.4947</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3946</v>
+        <v>-1.3295</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0421</v>
+        <v>-0.1653</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1709</v>
+        <v>0.3611</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4501</v>
+        <v>0.824</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7208</v>
+        <v>-0.4629</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2903</v>
+        <v>0.4103</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8691</v>
+        <v>0.3183</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4211</v>
+        <v>0.092</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8806</v>
+        <v>-0.0491</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.581</v>
+        <v>0.5057</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2996</v>
+        <v>-0.5548</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2588</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.2855</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2844</v>
+        <v>1.1914</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.283</v>
+        <v>0.825</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0014</v>
+        <v>0.3664</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>-2.2259</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1786</v>
+        <v>0.7207</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4189</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0368</v>
+        <v>-1.6135</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3612</v>
+        <v>-1.0861</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6756</v>
+        <v>-0.5274</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9879</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1297</v>
+        <v>0.553</v>
       </c>
       <c r="T10" t="n">
-        <v>0.12</v>
+        <v>0.395</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0098</v>
+        <v>0.158</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0514</v>
+        <v>-3.0992</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3673</v>
+        <v>-1.4448</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6841</v>
+        <v>-1.6544</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5517</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3909</v>
+        <v>-0.4387</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2362</v>
+        <v>0.1588</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6272</v>
+        <v>-0.5975</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6982</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0623</v>
+        <v>-0.7448999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3826</v>
+        <v>-4.065399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3203</v>
+        <v>3.320200000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-7.6857</v>
@@ -1390,10 +1390,10 @@
         <v>19.5075</v>
       </c>
       <c r="S12" t="n">
-        <v>0.116</v>
+        <v>1.4334</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2769</v>
+        <v>2.5942</v>
       </c>
       <c r="U12" t="n">
         <v>-1.161</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.306</v>
+        <v>4.9407</v>
       </c>
       <c r="E13" t="n">
         <v>3.4172</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8888</v>
+        <v>1.5235</v>
       </c>
       <c r="G13" t="n">
         <v>3.9953</v>
@@ -1468,13 +1468,13 @@
         <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0999</v>
+        <v>0.5347</v>
       </c>
       <c r="T13" t="n">
         <v>0.3176</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4175</v>
+        <v>0.2171</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2822</v>
+        <v>2.643</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5525</v>
+        <v>2.1801</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7297</v>
+        <v>0.4629</v>
       </c>
       <c r="G14" t="n">
         <v>1.9176</v>
@@ -1546,13 +1546,13 @@
         <v>0.616</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1942</v>
+        <v>0.555</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5851</v>
+        <v>0.0425</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7793</v>
+        <v>0.5125</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2402</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6259</v>
+        <v>2.2702</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3254</v>
+        <v>0.9079</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3005</v>
+        <v>1.3623</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4655</v>
+        <v>0.3435</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.184</v>
+        <v>-1.0481</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6495</v>
+        <v>1.3917</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2434</v>
+        <v>0.3713</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9402</v>
+        <v>-0.6939</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1836</v>
+        <v>1.0652</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2221</v>
+        <v>-0.0278</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2438</v>
+        <v>-0.3542</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4659</v>
+        <v>0.3264</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6427</v>
+        <v>-2.4641</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4622</v>
+        <v>-0.4039</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5461</v>
+        <v>-0.1861</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0839</v>
+        <v>-0.2178</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6982</v>
+        <v>2.9466</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1786</v>
+        <v>3.1868</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4595</v>
+        <v>1.4533</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3848</v>
+        <v>0.2208</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0746</v>
+        <v>1.2325</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3435</v>
+        <v>0.4655</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0481</v>
+        <v>-1.184</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3917</v>
+        <v>1.6495</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3713</v>
+        <v>0.2434</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6939</v>
+        <v>-0.9402</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0652</v>
+        <v>1.1836</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0278</v>
+        <v>0.2221</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3542</v>
+        <v>-0.2438</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3264</v>
+        <v>0.4659</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4641</v>
+        <v>-1.6427</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2146</v>
+        <v>0.2896</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7091</v>
+        <v>0.4415</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5054</v>
+        <v>-0.1519</v>
       </c>
       <c r="V16" t="n">
-        <v>2.9466</v>
+        <v>0.6982</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1868</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1894</v>
+        <v>1.3166</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1653</v>
+        <v>-0.8515</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3547</v>
+        <v>2.1681</v>
       </c>
       <c r="G17" t="n">
         <v>4.6021</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6899</v>
+        <v>-0.5627</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5774</v>
+        <v>-0.2636</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1125</v>
+        <v>-0.2991</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2736</v>
+        <v>-0.1947</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0056</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2792</v>
+        <v>-0.1947</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1355</v>
+        <v>-0.1947</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0014</v>
+        <v>-0.1947</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1341</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3812</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.618</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2368</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7542</v>
+        <v>-0.1947</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3833</v>
+        <v>-0.1947</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.6427</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1216</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7781</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3434</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>D. BAH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1947</v>
+        <v>-0.3386</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.2506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1947</v>
+        <v>-0.0881</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1947</v>
+        <v>1.1356</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1947</v>
+        <v>-0.2434</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.379</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.6399</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.7498</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1947</v>
+        <v>0.4957</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1947</v>
+        <v>-0.1335</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.6291</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.4475</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.0156</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.4318</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BAH</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4049</v>
+        <v>-0.7864</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3771</v>
+        <v>-1.947</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.782</v>
+        <v>1.1606</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1356</v>
+        <v>-2.1355</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2434</v>
+        <v>-2.0014</v>
       </c>
       <c r="I20" t="n">
-        <v>1.379</v>
+        <v>-0.1341</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6399</v>
+        <v>-1.3812</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.11</v>
+        <v>-1.618</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7498</v>
+        <v>0.2368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4957</v>
+        <v>-0.7542</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1335</v>
+        <v>-0.3833</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6291</v>
+        <v>-0.3709</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0267</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0534</v>
+        <v>-1.6427</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5138</v>
+        <v>1.0616</v>
       </c>
       <c r="T20" t="n">
-        <v>0.612</v>
+        <v>0.8367</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1258</v>
+        <v>0.2249</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.788</v>
+        <v>-2.1943</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6933</v>
+        <v>-2.1117</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0948</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.7702</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3022</v>
+        <v>0.896</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8173</v>
+        <v>0.3989</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4849</v>
+        <v>0.4971</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3963</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8906</v>
+        <v>-2.7918</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0926</v>
+        <v>-3.793</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.798</v>
+        <v>1.0012</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6392</v>
+        <v>-2.5748</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6392</v>
+        <v>-1.3143</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-1.2606</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-2.0106</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.655</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3556</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6392</v>
+        <v>-0.5642</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6392</v>
+        <v>-0.6592</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0461</v>
+        <v>-0.6276</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0659</v>
+        <v>-0.345</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0198</v>
+        <v>-0.2826</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.796</v>
+        <v>-2.861</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4206</v>
+        <v>-1.0926</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6246</v>
+        <v>-1.7684</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5748</v>
+        <v>-0.6392</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3143</v>
+        <v>-0.6392</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2606</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0106</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.655</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3556</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5642</v>
+        <v>-0.6392</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6592</v>
+        <v>-0.6392</v>
       </c>
       <c r="O23" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4107</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.4374</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6318</v>
+        <v>-0.0165</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9726</v>
+        <v>-0.0659</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6592</v>
+        <v>0.0494</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.062400000000001</v>
+        <v>3.456999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-3.3204</v>
       </c>
       <c r="F24" t="n">
-        <v>5.382599999999999</v>
+        <v>6.7773</v>
       </c>
       <c r="G24" t="n">
-        <v>7.685599999999999</v>
+        <v>7.6856</v>
       </c>
       <c r="H24" t="n">
         <v>-2.7595</v>
@@ -2299,10 +2299,10 @@
         <v>10.445</v>
       </c>
       <c r="J24" t="n">
-        <v>8.280999999999999</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1756000000000004</v>
+        <v>-0.1756000000000005</v>
       </c>
       <c r="L24" t="n">
         <v>8.456499999999998</v>
@@ -2326,13 +2326,13 @@
         <v>11.2938</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1158999999999999</v>
+        <v>1.2787</v>
       </c>
       <c r="T24" t="n">
         <v>1.161</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2769</v>
+        <v>0.1177999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>2.706499999999999</v>
